--- a/public/recursos/plantilla-atribucion-resenas-google.xlsx
+++ b/public/recursos/plantilla-atribucion-resenas-google.xlsx
@@ -89,7 +89,7 @@
     <t>¿Demasiadas reseñas para llevarlo a mano? Atribuya hace esto solo: cada comercial comparte su enlace personal y cada reseña queda atribuida sin Excel. Pide una demo en atribuya.com/demo</t>
   </si>
   <si>
-    <t>Un producto de Castillo Cantón · atribuya.com</t>
+    <t>Un producto de Castillo Cantón · atribuya.com · alejandro@atribuya.com</t>
   </si>
   <si>
     <t>Comercial</t>
